--- a/backend/data/Plantilla_Procesos_Refax.xlsx
+++ b/backend/data/Plantilla_Procesos_Refax.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://refaxpesa-my.sharepoint.com/personal/avargas_refax_pe/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{002E23C7-F12A-4EA4-BBF1-650EE9A08F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DE63096-172C-4C20-9F09-B16613E2A151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{FF44A531-1A9C-463F-8074-9DFBB8A8452B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="DOCUMENTOS" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DOCUMENTOS!$A$1:$J$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DOCUMENTOS!$A$1:$J$252</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PROCESOS!$A$1:$J$237</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3538" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3733" uniqueCount="1368">
   <si>
     <t>BI</t>
   </si>
@@ -3605,6 +3605,570 @@
   </si>
   <si>
     <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCwEAviwcq9TKcyTawLfE5sAWsTGjyoZP1xV_G8OwoZ7mk?e=8ZUfUg</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDzH38vAOZ6R4kcDGpbCUh9AZNoNvXlKINOMPo-hIDpLnY?e=9oA2Gb</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDbrbXLqr1ESLags8_GPMk3AUtuPG1ZwVKjxgdshhM7upw?e=ggRUqT</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBD6EB-zfzdQrbpxxFggUv5AajWozx14uykmhSlxblE1sg?e=eUuq0H</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA68qKsLUNWQojAMvvM9vRAAfcFhjSySH7OTHMwZDDCJxs?e=iq9XSB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAO6e0VaJdQTYSCoGiE_99qASid6DyeElCCWRkT0viAEgQ?e=Dd0nWf</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAq-Pp6yrNQRK59EC_zdyEbAcGD1EYMR0DadFMRuCJ_xpI?e=sX1vj0</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDqlaX2WyJhTboSeF4AHy1IAajVhE-PsUFG6bcfnSSlVJk?e=VEYtuB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDXRRbRgskETaPM0KjX5uiCASayLh2H-J2MiMW5jtSzaoY?e=c1LM2a</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDWbk6iBup0Q5J1MqYrsqp8AcZ84arVTLkQVGjYNooyl2Q?e=GbH7pQ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDbBAJaiY1XQb0WkTQEvibpAVdoxGBTrR0q1Kig-uLKnSU?e=XtBWCf</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC_7tD_H0T0QqFrqd4cZ2_tAfc0qfhbm70yBamJpQ0a6dE?e=PCuff4</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAWgM9KuXcvSKqVzUK_en-cAWAt-m2oSKT7HEJMMIrxopA?e=lMU4h8</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBtCU3tQ88TRoR-_6EjuKqwATEMeqwfvaRplWcbw_03mB8?e=aXymPB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCMabLly9xFQpttvRBRyicQAWxiaoV18evf2GbyJ3OC-PM?e=3ft0Cx</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA6ry23r6WbRJjjSIazqLDGAR2nAEJ7a9OHxKT2DffjMso?e=h5GPlv</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAZXWQTRL8GQpyThorl4bU6AXsE3RVOBFlm1eaxp7Dvzdw?e=jEIVx2</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB2YBIJ8bN7TbrmvnFdyTNDAYExLSw4hH9PROdVSaQ8EmQ?e=acDELc</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBmmPnqysHXTZINufS5NHkXAVxINbtJx4OOp1WZ_OUdQ7M?e=sAqVXv</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCPifDzCznNRpvqMrzoT-aVAfm50-jxL25sEGPDlo48luY?e=amLvD4</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBUx7XmOHBYT6wBGZd9br6oAWtdE5WJmFzuHOlQbRwZGfs?e=BRzTYu</t>
+  </si>
+  <si>
+    <t>TI-092</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAbXxalMtrqSIILNYT_tKLuAWge-dygGG09FIkpXrLWH_8?e=Unj28x</t>
+  </si>
+  <si>
+    <t>Guía para la Gestión de Archivos en SharePoint</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA05BOkrGNZSrPzg5XR-VJsAZi0LaoXPPkjF8UeT-4LP_A?e=G3ceqa</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAEHFPNjOmzQJgHTcCVXq6xAe15DceXmTcK0oui2k5y8tk?e=0WlSCJ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCnnB10p3dAQqyS3dSA1BwJAUdN20ar0nS4PAppH8gEMaU?e=GyU2gf</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB9g5pfaz7SRqW0dGaIkWVRAT_t0hPOxvRD9Arz_LVnuUU?e=4G67NV</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCb46Ib-SvCR5MWZaf3bkd5AYWopKJeDDUBhF38bZHXX1g?e=Qz8lSN</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQD5PRH8rZ5ITYS7uTJU7SXOAYAOMW_7MVCApYLNO6c4kKg?e=tV4F58</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDFuuwbBmKSSrz19wPKj37mAXl5_NMskXRyj9uOh5BinSk?e=AoqGfL</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAgc0crF3FyTrBj97WtkGW9Acu0D5nwAY8ir17YK5v8jbE?e=JYft68</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBUd0lpeB7MSpU83hah0eprAXraDV9TPSxRVXLKBgXdnOQ?e=4vdk2B</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA5rL3j7vHNSo4HYtp3cq2sAYFCnznt37PjIwsNbxxq6yE?e=pa52kE</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB316M7wQ5jRIxHO4HqG0vbAc3vOKSfjBCL4ufFOaDPrlw?e=O965Hc</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCraBWq9UceQJKNy4oAMhnBAVpyqJFbTH9BGRgShBSihho?e=s6fqfc</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB9QmxD7fslQb42CmLK2mbTAQ0PjQ1-B5VbAHT_IS52kTg?e=DkDAgR</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCTccamu58tSYXAToupRZFvAXwxLwbcKZbavOYbi2bGNZw?e=p5Cm3g</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBm-A15USZmTaBlDeRzbHebAQ8FGsbzCnQ7xHY2Mj90Gtw?e=W0aKHZ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBZX4GwR2vLS4UdNBGzzr-cAXXhqJOt3o0XC4uaElG7DFk?e=j8rDN6</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB-N38lWF9lS7xIxxdTfIWbAV7XbO45mmsnrgZCCp7UWMg?e=Nz706L</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBsT17f-MXyR5BnMhfQhqrlAVrNKRKqmiEykhYvRjzJFZw?e=rGr8UB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAYC4cvzoN7S4wUCyODNcXfAT1Q9oJ1ltoLPxpnBkjAtho?e=ZVyICH</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAn91HsNTBSTq4qU_Tz7nI8Ac2AAits6No_2NsMkcAIh6c?e=8nm2gv</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAewIOpxoaGR5TsKAcVuiPSAZJLbN9RqJyzWg9bwpVf8dU?e=R3JoXB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCO42-7NxajTqMXJ9SH8f4dAYRQjZap6uPAaMLqWe1mpd0?e=ozLui2</t>
+  </si>
+  <si>
+    <t>Manual para Cambio de Número y restauración de WhatsApp</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAaMwuJdUiUSr8j6zmUJDdmAQne5wkjdOGkES9wpVzLKEM?e=mRf0aj</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBEwhLGlMqLQ7zuEyS9XDuuATw4BQCQr0thepuHtNVZCuo?e=xeGsKR</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDfR_60QSumQamJefhXsP-CAUaPMbi5ihFBMpReJaC597Q?e=vWFNBB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBj3A1rszfPRL1_p0fxuGfUASFqTISAaaibFaMuTNlmW4Q?e=9U8ARr</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB6Yi2wRjNfTa9isEcmqxAGAYikgW6h-19-ykbWE9ofGLQ?e=6zS2FF</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQClb4srF7AOQptw69RpsMDuAdBOmSyk_7TYDfFNtpQUhgg?e=P5ey0L</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCESl2OetsvQpSyIn4kWFdtAVaJ4KvL1BPLwKsVMj8VYkc?e=fcQhUp</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAwfGD7-bh8RrZpmzOCRZvxAbzdoC0dmFMTwsiugsCG7f8?e=WzP6fQ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCOxkSwcjMCS72KfCvH0EdPAZMWiMbuemi3-Le1qffdFSk?e=yrNimZ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCf0Ul4ZHJmTKYV6ujEo09-AWRLyu3iZ6oeNWllel3-ONs?e=xAap5u</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQADbyR-LBn0TLoj9AEbg2FwAbz4ME4CxdRIUhj0at2a3A0?e=jpKqyO</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBI5n0OHbj2RYZFDjhbPC8BATmqrClJSZQBQqJxGL7uh_k?e=QqL7lN</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBHdOJCXJllS4UfmvoaijuzAV6ZKqROt3iBNydMIzg14Vk?e=dIRS4w</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC0SdUeVMUGTqfc3WhGQDcCAelXCqLOYvazw3fkOOuzPMU?e=w3ICX6</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB86WQedNeiS7gQgMNYtN-SAatM7V4UtGVzBt9us2R-Ta0?e=YbjWe0</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDVf8ezcU0NR5bHrsTlwsp4AQvFTjGOSy_9hX7twKVqE1w?e=aXNMX8</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBhL98lwOvPSKpuhRVtbZeAAfI9XvRlLFUrpyh_lQDbd34?e=suNafL</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCywe-sGsHISbAZcotdfiovAeJ4SnLGOPwi9EJk9lG8AWM?e=NfeCJB</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDwDUL4nBUbT5BuCvLRWNJRAcNhkdOfxO-FQUheh2-9Zv4?e=epjW7i</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCcoNPXz4V_Sr0oxMTqqkxDAbYY4Pl2LIDVyJf-_IU1t3k?e=wfnc8f</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBWzdZ0S_kEToPCF8gbCjBEAcXLTZacP7zy7JQd_mANk6E?e=FTTXjm</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBg9caX-HGPR7SOcTm-9EcdAfDQtd46883YEpEHCiIKChI?e=5mObYl</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAcMopKaR9qQ5eG-fnEmO5BAcrKb0yHWANl5uxPpgZmzvU?e=5JkAcY</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDPt1FZh-7BS7Az6N3OIfYEAfv70wLGSbnbxaOAxqFnBl0?e=L4mRNd</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC-FVCsKupsQpaYz43oYoYGAc1M0zrwrlrQUic-lCsa6qU?e=cqWOOR</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB8DwTv7nmIRbWbap300SkUAY-rVsdBaWH-hDw5hUzel90?e=gvYxxe</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB61kZdp1xTT5d01FJ7yUs6AeKp0N4cgDDKbR6BoWAJmPk?e=Oz47BH</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDLg9AKUclrQ7U1tkjmU7qvATiKTQT9_Q5FkeTaedPUfFc?e=GxvYCC</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCvlKmepJKlQqFBGC7xyjM8AeMcDEUtmNCnVMWSzDI616U?e=3vwkQF</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBeiNlsVseRRZDKNELKxktVAZDoZtXrLLOqYF-Pa27oc2Q?e=S1xsok</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBsDsC0nf8DS7DYyPKtiyZaAZJTQCgtoAuqXkvUdVNE9Os?e=TXDOtK</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBkXVsgzqLbQLMjW5_tkCoIAcDTy4cgJk844hO2tU0KhY4?e=7pdGwg</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCuZZTePxRtRIsJ74lAmp5RAf7Begc68pzTkap8t0WvhAs?e=CgTXqK</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBx222dPnNdRbu7wBUkJXA0AcXEooVuoKA6F5LjSnY4Ocg?e=0RDhnA</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDinfOUMj9OTLfkNZzFYSx9AVM43FN1kCGQb2NMuyWG0ko?e=hCfZgQ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAZ7c03PxEAQ6NHCuF1MUtLAfKFliMhJGebPV13KE9X160?e=E95jqm</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA0Wo6YOlKXQpw643Ioi1AoAUSS-Jwn1JI9qaU9W7otqck?e=AODxX8</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAzvxM_zmrGS5ram5WSiw6DARjFmaXuoXyPyPZiq1wvDKQ?e=xnGhLU</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC0GNmFW9lYQpYJvzdtPj0CAezp3IQr4ZuYEAqkcwlP3MU?e=THYbZ3</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBVdZMfoEJcRYSKepmiRFHXATI0lAcmtysNa4jALbfZibM?e=mMFvbS</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCHvkcAbXzpTYJ4XEa61nkvAWoNYrlx3NLBiODDjLA5oEQ?e=pYC9lh</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAAMqFQQt08TK2Mpk2KsxcZAYPGmenVwsjI_RpftbWoLxs?e=duznWD</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBJppQK3LgWQorDZ5F8eUEPAaFEyjx2DDJiDLPgIvFWLdk?e=p0L6RJ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAh0e3h51wpR63TTnoHpxnhAbzudIUJRTeEbs784d8-ios?e=VIwVQK</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDxpnnoOwgWS7uffj3uyOrsAeV5Zz8A9Khe_1Tr5QXV4C8?e=lwwcHV</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAwGwQirX4kRZWe8h29cQ-dAdwnSzThI97Fro4j-xHve_A?e=OGMspX</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCfT941jzb8TbcKm_SSS44mAXk7Gqk27oszASwV-zZ7U1A?e=ro7lCU</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCmpKpkamaRTLRgAApqXhNDAT9WLF_nDrOxSMFI6JwbO1Q?e=Y0qNYn</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCdde9tiI9xTIpJnKP_r4puAYG5gBsKW8Lpqi015Lj2rSc?e=5ZRENS</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDy7hpASeE1SKDPPJnqqqnwATfO07j5N7vOQwvHKrRgzTY?e=xrCdPP</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCzkKs7G8lzTr1xx3GiIm3qAUdxcSGKmIrFRm0I458aNlM?e=jEaaHg</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCQ2mrePgoKQ7VtBu7mJPbnAcnpIYN3BwHOejukl7CO5oU?e=I8vUXp</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBST7sVSROcT4cPety5_CYgAe7hvdNngVPsG40XjkjSXiA?e=edizJw</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCC47HrosEYRqyVpccIga8iASjMnoS_qgaiYOYHQ76vWtA?e=DFLUpx</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAEgNN7VINbQIcDMeWgH8RSASy0F3RWGO4jitdmTrhnCb0?e=1Kqsef</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCrGF5RMAukRZ-0Wen3e84nAWZB3o10bNtnkwWVa2bvg-E?e=S6OA0N</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDZ231wFDhOQavnYpquucG7AYFcB80Tm_PkXAnMA-_VNmY?e=WTObqu</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDZUtJVnTXIRbJu0Q3bFwPpAcTzwYW__MhqYXv8kONRQDw?e=lyKda0</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAu11qukheGRJjbkuKNZXUaAaNCZdkBXV8cym7RNAeKKXM?e=tgIWUX</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAptM-RfN0kSqJhkDb-jsIwAeIOJPqUC4Y6HXeJur6g4ys?e=vMAFmX</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBzxPLP79QgT48DR_sllTCNAf3go-tSU7LGzaO-AqzYppA?e=lrdGAF</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBkaoOyoIWuSK-Y2S3m6lFyAXVU7szLfFnmyfOpI7f-yWg?e=tzIGYh</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQChrgsIJcB2RpyZyvJK_csjAUr1Gx7PJatkGbfEpxs1ll0?e=wEdneJ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDVHsaltfxAR4AmZCmUV4AmAZdBxaCc-gCcaCTKe5YL1Ns?e=00vjTL</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB8zp219LepTqBAL8DscHsyAey8b_iByo88-5rAu98BEMQ?e=lMdC0E</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBH_gxVp18nTb5JlSbwbdhaAbTEuDeJ9d-xcWlVFpMRbvI?e=HHz0jE</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAKRBRekq_1RrKjgeIknIeyATJQq5UTFxw50cOTkOoZAPU?e=L0y2i5</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDAe6IWR_8BSaZpxVtYdiHIAfgorRSGFeiODjUQN_gVVnI?e=Xvas3N</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBD6aI5SldRS4BCmxfT1F4QAWkBiZOIqaEr1yN7Fp3QDZ0?e=rZQcb8</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAdk9dwXdTcSpKYOzsdEaisAZol4B7RrW9DE3GB5cAt7w0?e=0ilmoA</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAbSVHLz2jaTbCSIP07jl4TAb1LDl1O5b6tphD-7vSVWR4?e=9Di8ig</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAQHq0YAf07RYz9aoGoRnaoAY_jXG6ugWReFAjn-OoQm2A?e=bxZvdE</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBiFErY09LjRZMCeRPUoRVpAVV1yCmfHvU_2aBkB9d4smQ?e=kDlkKq</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAsIZL5J-XpQ4sUfTVKx30FAUInOGceLTxtmVyYQnUhvy0?e=Ms7FGh</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAOZLtfUEJFSYmWuxw9s04lAUFad7jR9op7f86u_K0cF24?e=BXI6kg</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCmSsI8cTdrQJoKKeH1PNjaAeK3c2hyHeMUjHw0yrU5XlI?e=cOm1IG</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBG5OjgP0CpTpP3MKmeiJ5VAabm_w9IrXHkRpo1wJRfrrY?e=XtssJX</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAeYxjQ8wP3SJPvPjokQ3xgAa3DOoKCOzCQPODOeh4qelc?e=IMD8X4</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBvtjBqDxLhSoteaEIKfrD_AYa9zM1G0pc_LDt0JaYZq-s?e=vmL9jI</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBAWajBsEC-Tq2X0aAhKhYKAeeP4PJ24o8tTOvxZO2WZQw?e=ZWSCu6</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDxgme-9osKS6T0YHiC-cw1AVk_JrmWkwdlHL8--Gxo3Sw?e=Sy7HOF</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDj4I6G5PUKRaPYOlMaKs7wAcgRGlxkihYuwyHnCLjfPps?e=VubjDi</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB1azeBctPcTKOOzgKEch2DAeeSUXdW33XtH9WziMpxKes?e=92YrxI</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBTy5jxBMJbQ4aC8e0H65CfAc8ff-FSoSPhbyE4P6SmwBI?e=00ujnt</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDOLaUPtiXtSr55eVoHR_cxAcETYARalZSH0YQhxxO7Ol0?e=6Yjlwh</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA98Ih8LMvVQ53rT6uacFTWATBiYY6mUQznOYK2AAmQ-z4?e=uS0YH5</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAO6wuVlGk3T7B2OghqgEd0AUFSUuo8PojunmnKxhAL2Mg?e=Vk5r4H</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCvvnQetKj0TpxY_CNGe7TuAfnnt9dMzdFOP2_wjzYoTf0?e=UqKmp4</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCrn4HiPYDIS5GgbTpR2msNAZFp9dUHIC-o6P24ilB8xss?e=ksRryy</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDXIwZSHD7dRJx0Soo25QzFAaKTSic28ctWhglA7Nx7T8U?e=tks7FJ</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAort9hGBZ5QIa4X4ojRVgBAcG0aqGUTszMm8RvlAM6QnM?e=uiCaMW</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBKgcznIMmzTJNXHxOV0IddAeQ6BWvVJ5omBQjjP85lb4o?e=suJDyU</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBhH790Wb93QI-MWaWodUfOAZYrcBqpMYaPSKxyLzf6UiQ?e=8cDGUm</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQD_iNp9LCxkQYfFpoNW3k7oAR3KmOWyilC8hqIUbIhU9I8?e=i7Co7I</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCX4l0w81HITqlyoYKK4aJbAWAf7gcQrgogIpE7E5AD92E?e=MV8wwz</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCOESBCN6KFTpkFXF7wb_0vAV_8463YxhI7bWpSdME-Us0?e=opLKrd</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQADmvZ6daFaRJ5EN95gQc9FAV2t5mCUIfGMwUnwfzzEJsI?e=EAQVkn</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBg1y7K09yLT7TSilD4_zWOAS7yia4BEOrYc6405t3XUv0?e=O5ypY4</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBwrKN6d6cRSqpHr-0hmTW_AaG8EXTdS61XnzL8D3LdHZU?e=S4qWN0</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDAGg2XW4lsSIvy2koewuwoARimmv4zEbtUheMKIAmp1UA?e=Kfrkig</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBBPKjnINOKQZGkbiWZrav-AXQ9eYY6Dr-RuVWnPFbloc8?e=emTroz</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBdnvzpN2sYQqjLIiZiiOnPAQL41_tjrnYzXbfFl_goMs4?e=YAdALx</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCb_WpVocVoS7KOxHjH8WCtAR7WmE6eSlTohTSPGtyrqQA?e=k72PUV</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCR1NnMfkaPQ4Lzzg9uNa2DAWFjZnDQwO6To4Mo6R03x6E?e=ZMTh7g</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC93_T3htAhRqwXXZ4vs6A6ARaNrbGKwTEUoTMW1YKJfg4?e=LaGNfC</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB7Xe2g3gjGTYkRlH64D09YAdPTJeJwOZ4YgeqSSzFk2FA?e=m4zLo0</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDbBwmMUpssQJqNprhZMB2bAacanYpROcxpTfYKgHnRQW8?e=wQVhJC</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBvyCZ2Wr0mQqGfLjJlukIgAW4vQJxeOfnzga2feNCZVw0?e=o59YcN</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCRUBa7tWWOSKd20O6sqCcfAZT_sDiVS-j0yThJkUT8cto?e=Yy7i6b</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA_Ls9GBQuPQYvJGsBuRJ86Ae282cO9LlximuMOpNupsX0?e=Ovcr0R</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDCMYIl5pK3RIA7GMLudWoDAeVn2wHqJFSkNc3bbRTA5pE?e=XV26hb</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB9WOFrypoaT6BggLRyM65xARpTznvPsQuTK_DgMNiMHOE?e=Sgw7Ii</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB4b2cWTgmFRo81JlJJX8owAbcJH_eSsK4CCetvXW_fbNo?e=2JhwPE</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAYjSD0tK_zS7Wexu_Rn7t6AbmaGLnrTTMJ1BWJ_aqTXZk?e=RtyDGc</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCN7LYpARQ3Q5ezt-YrT-TyAVvTfo2qBPvYOOrBnJ07gdE?e=afAuHW</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQD34hs70qSmRKhmNEwDIWdHAWrzB-2Q9hLbMI9HRI5EQes?e=tGB8sy</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBQncGG0E8ST6t4tpmemlmFAXWks9KCHzfuX4P4cj5r8Rk?e=OwDUxv</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBoSccS8oddRq_NhHrF_zcRAVlzFPvor8xDrnchtCvvG4A?e=JgxpHR</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCYqnyRRjnCRYvEd8ptYXyDAWCliT30qnT2h6orJUo5ZDA?e=9Ze8zG</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDGApGwVgyNTKXRx-QPaWbXAbcWmi64sk6gMxVYsp-Nc30?e=vHywOV</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDQBuiebgZ0TJklW9aJlw5AAYnS3YCI7aZffy-5HRgWbF0?e=0mSIBr</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA7aOrByl01Q6YtOR9hPcJIAZEluEdnkaE5wyAbyicLn-Q?e=yDdDa2</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDk13PS-3rUTqygtdVduNeqAR5Hri-yvpJbfFQoaRXjF_o?e=AnrXeU</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDcQzp6_hxTTIyRSFjdR9ZhAd5V7uU5gTrzII4gy9Npb9I?e=57qGka</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBCW0AUNlBaToBVwGTaPUrfATmiMMMRzXJR1doKJp3g4ek?e=i26un9</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCz0saaL_WpS5qaBTYLVhJvAZvRJrLMFX2KBCamKDEy99o?e=CZ9QSg</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDKDp3TVh9WQpH6ixCnTjqSAdE9uQDbn0Jj4H2QsXQ3CwU?e=xeYAhM</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQAWkLJxUsROS7Tzl6Ug0czFAV14-RbB-MI5WISKldzyf0I?e=kql69R</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBz7bvzJ3ioTbppTZ-8sOSrAdap5o5Y3WW5S_QuYvoN8ds?e=qmAnDc</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBvYEgakv4BSI1KbgqxP2RQAUOuxAwZf6eJScI1HLlIV0s?e=VgrdIq</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQC8M2RcUxNdTYFVBFQqwvfmAa7CD2v7oBFG2xQ1Br5kgII?e=z7rq99</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQB8iZnkNdOTSLfQCW1F0ihqATkYN4SZfaoWBt6Vo1hFJjk?e=yn0TAt</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBzDJO5HE1HTasts0y_xg91AS9RZ7_bILXCb_UVf2Fwk74?e=lT34FI</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQCp2gOFU6GUTbS_wrj5lWdKAfa96WR8c2WGAZA76Zjcfos?e=ziY17d</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA2Bqp-8fVdTbhbvVHy1c9QARy6WbpjhmhJI3wtWxGWG94?e=GfRdg3</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQA2Bqp-8fVdTbhbvVHy1c9QARy6WbpjhmhJI3wtWxGWG94?e=cNM45q</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDFmo3c1vtFQ4FzlIP60MP6AWcmCiSGamBIgXaPIEuwiaA?e=SEWl3b</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQDrC8fjg5_ZQIV7nupcTC4XAQYg_K-5qBG4kuHAB_0TDpM?e=3apftM</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBh8UbfD9W_TIMNqkP2qG38AdYkQvpvytd_E88y1ijwHTw?e=SF1TVt</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBiqvC2G4r8T57ueT2Ebx_2ATzP2Wf3b8uEDyRKMgJ-1gg?e=JYlI3R</t>
+  </si>
+  <si>
+    <t>https://refaxpesa-my.sharepoint.com/:b:/g/personal/avargas_refax_pe/IQBFi2RrrkpHQYtPL-NzTXkTAakHIga-D1PjRhnvIMePpx8?e=5YSIvX</t>
+  </si>
+  <si>
+    <t>TI-093</t>
   </si>
 </sst>
 </file>
@@ -3678,7 +4242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3712,6 +4276,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12054,7 +12621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748BF04F-CFA1-4A20-9F03-257823D17D54}">
-  <dimension ref="A1:J250"/>
+  <dimension ref="A1:J252"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -16237,7 +16804,7 @@
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
     </row>
-    <row r="163" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>588</v>
       </c>
@@ -16253,13 +16820,17 @@
       <c r="E163" s="8">
         <v>45743</v>
       </c>
-      <c r="F163" s="10"/>
-      <c r="G163" s="10"/>
+      <c r="F163" s="10" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G163" s="10" t="s">
+        <v>1180</v>
+      </c>
       <c r="H163" s="3"/>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
     </row>
-    <row r="164" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>591</v>
       </c>
@@ -16275,13 +16846,17 @@
       <c r="E164" s="8">
         <v>45743</v>
       </c>
-      <c r="F164" s="10"/>
-      <c r="G164" s="10"/>
+      <c r="F164" s="10" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G164" s="10" t="s">
+        <v>1182</v>
+      </c>
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
     </row>
-    <row r="165" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>594</v>
       </c>
@@ -16297,13 +16872,17 @@
       <c r="E165" s="8">
         <v>45742</v>
       </c>
-      <c r="F165" s="10"/>
-      <c r="G165" s="10"/>
+      <c r="F165" s="10" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G165" s="10" t="s">
+        <v>1184</v>
+      </c>
       <c r="H165" s="3"/>
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
     </row>
-    <row r="166" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>597</v>
       </c>
@@ -16319,13 +16898,17 @@
       <c r="E166" s="8">
         <v>45743</v>
       </c>
-      <c r="F166" s="10"/>
-      <c r="G166" s="10"/>
+      <c r="F166" s="10" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>1186</v>
+      </c>
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
     </row>
-    <row r="167" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>600</v>
       </c>
@@ -16341,13 +16924,19 @@
       <c r="E167" s="8">
         <v>45701</v>
       </c>
-      <c r="F167" s="10"/>
-      <c r="G167" s="10"/>
-      <c r="H167" s="3"/>
+      <c r="F167" s="10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G167" s="10" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>1189</v>
+      </c>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
     </row>
-    <row r="168" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>603</v>
       </c>
@@ -16363,13 +16952,19 @@
       <c r="E168" s="8">
         <v>45701</v>
       </c>
-      <c r="F168" s="10"/>
-      <c r="G168" s="10"/>
-      <c r="H168" s="3"/>
+      <c r="F168" s="10" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G168" s="10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>1192</v>
+      </c>
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
     </row>
-    <row r="169" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>606</v>
       </c>
@@ -16385,13 +16980,17 @@
       <c r="E169" s="8">
         <v>45720</v>
       </c>
-      <c r="F169" s="10"/>
-      <c r="G169" s="10"/>
+      <c r="F169" s="10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G169" s="10" t="s">
+        <v>1194</v>
+      </c>
       <c r="H169" s="3"/>
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
     </row>
-    <row r="170" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>609</v>
       </c>
@@ -16407,13 +17006,17 @@
       <c r="E170" s="8">
         <v>46087</v>
       </c>
-      <c r="F170" s="10"/>
-      <c r="G170" s="10"/>
+      <c r="F170" s="10" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>1197</v>
+      </c>
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>612</v>
       </c>
@@ -16421,21 +17024,23 @@
         <v>585</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>613</v>
+        <v>1202</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E171" s="8">
-        <v>45743</v>
-      </c>
-      <c r="F171" s="10"/>
+        <v>46289</v>
+      </c>
+      <c r="F171" s="10" t="s">
+        <v>1201</v>
+      </c>
       <c r="G171" s="10"/>
       <c r="H171" s="3"/>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
     </row>
-    <row r="172" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>615</v>
       </c>
@@ -16443,21 +17048,25 @@
         <v>585</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E172" s="8">
-        <v>45720</v>
-      </c>
-      <c r="F172" s="10"/>
-      <c r="G172" s="10"/>
+        <v>45743</v>
+      </c>
+      <c r="F172" s="10" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>1198</v>
+      </c>
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>618</v>
       </c>
@@ -16465,21 +17074,25 @@
         <v>585</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E173" s="8">
-        <v>45721</v>
-      </c>
-      <c r="F173" s="10"/>
-      <c r="G173" s="10"/>
+        <v>45720</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G173" s="10" t="s">
+        <v>1204</v>
+      </c>
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
     </row>
-    <row r="174" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>621</v>
       </c>
@@ -16487,7 +17100,7 @@
         <v>585</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>167</v>
@@ -16495,13 +17108,17 @@
       <c r="E174" s="8">
         <v>45721</v>
       </c>
-      <c r="F174" s="10"/>
-      <c r="G174" s="10"/>
+      <c r="F174" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G174" s="10" t="s">
+        <v>1206</v>
+      </c>
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
     </row>
-    <row r="175" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>624</v>
       </c>
@@ -16509,21 +17126,25 @@
         <v>585</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E175" s="8">
-        <v>46001</v>
-      </c>
-      <c r="F175" s="10"/>
-      <c r="G175" s="10"/>
+        <v>45721</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G175" s="10" t="s">
+        <v>1208</v>
+      </c>
       <c r="H175" s="3"/>
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
     </row>
-    <row r="176" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>626</v>
       </c>
@@ -16531,21 +17152,25 @@
         <v>585</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E176" s="8">
-        <v>45719</v>
-      </c>
-      <c r="F176" s="10"/>
-      <c r="G176" s="10"/>
+        <v>46001</v>
+      </c>
+      <c r="F176" s="10" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>1210</v>
+      </c>
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
     </row>
-    <row r="177" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>630</v>
       </c>
@@ -16553,21 +17178,25 @@
         <v>585</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E177" s="8">
-        <v>45971</v>
-      </c>
-      <c r="F177" s="10"/>
-      <c r="G177" s="10"/>
+        <v>45719</v>
+      </c>
+      <c r="F177" s="10" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>1211</v>
+      </c>
       <c r="H177" s="3"/>
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
     </row>
-    <row r="178" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>633</v>
       </c>
@@ -16575,7 +17204,7 @@
         <v>585</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>167</v>
@@ -16583,35 +17212,43 @@
       <c r="E178" s="8">
         <v>45971</v>
       </c>
-      <c r="F178" s="10"/>
-      <c r="G178" s="10"/>
+      <c r="F178" s="10" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>1213</v>
+      </c>
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>636</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>148</v>
+        <v>585</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E179" s="8">
-        <v>46100</v>
-      </c>
-      <c r="F179" s="10"/>
-      <c r="G179" s="10"/>
+        <v>45971</v>
+      </c>
+      <c r="F179" s="10" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>1215</v>
+      </c>
       <c r="H179" s="3"/>
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
     </row>
-    <row r="180" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>639</v>
       </c>
@@ -16619,21 +17256,25 @@
         <v>148</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E180" s="8">
-        <v>45700</v>
-      </c>
-      <c r="F180" s="10"/>
-      <c r="G180" s="10"/>
+        <v>46100</v>
+      </c>
+      <c r="F180" s="10" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>1218</v>
+      </c>
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
     </row>
-    <row r="181" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>642</v>
       </c>
@@ -16641,21 +17282,25 @@
         <v>148</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E181" s="8">
-        <v>45741</v>
-      </c>
-      <c r="F181" s="10"/>
-      <c r="G181" s="10"/>
+        <v>45700</v>
+      </c>
+      <c r="F181" s="10" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G181" s="10" t="s">
+        <v>1219</v>
+      </c>
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
     </row>
-    <row r="182" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>645</v>
       </c>
@@ -16663,21 +17308,25 @@
         <v>148</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E182" s="8">
-        <v>45887</v>
-      </c>
-      <c r="F182" s="10"/>
-      <c r="G182" s="10"/>
+        <v>45741</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>1221</v>
+      </c>
       <c r="H182" s="3"/>
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
     </row>
-    <row r="183" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>648</v>
       </c>
@@ -16685,21 +17334,25 @@
         <v>148</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E183" s="8">
-        <v>45720</v>
-      </c>
-      <c r="F183" s="10"/>
-      <c r="G183" s="10"/>
+        <v>45887</v>
+      </c>
+      <c r="F183" s="10" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>1223</v>
+      </c>
       <c r="H183" s="3"/>
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
     </row>
-    <row r="184" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>651</v>
       </c>
@@ -16707,21 +17360,23 @@
         <v>148</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>652</v>
+        <v>1225</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E184" s="8">
-        <v>45701</v>
-      </c>
-      <c r="F184" s="10"/>
+        <v>46290</v>
+      </c>
+      <c r="F184" s="10" t="s">
+        <v>1226</v>
+      </c>
       <c r="G184" s="10"/>
       <c r="H184" s="3"/>
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
     </row>
-    <row r="185" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>654</v>
       </c>
@@ -16729,21 +17384,25 @@
         <v>148</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E185" s="8">
-        <v>45702</v>
-      </c>
-      <c r="F185" s="10"/>
-      <c r="G185" s="10"/>
+        <v>45720</v>
+      </c>
+      <c r="F185" s="10" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>1227</v>
+      </c>
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
     </row>
-    <row r="186" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>656</v>
       </c>
@@ -16751,21 +17410,25 @@
         <v>148</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E186" s="8">
-        <v>45742</v>
-      </c>
-      <c r="F186" s="10"/>
-      <c r="G186" s="10"/>
+        <v>45701</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>1229</v>
+      </c>
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
     </row>
-    <row r="187" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>659</v>
       </c>
@@ -16773,21 +17436,25 @@
         <v>148</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E187" s="8">
-        <v>45695</v>
-      </c>
-      <c r="F187" s="10"/>
-      <c r="G187" s="10"/>
+        <v>45702</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G187" s="10" t="s">
+        <v>1231</v>
+      </c>
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
     </row>
-    <row r="188" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>662</v>
       </c>
@@ -16795,21 +17462,25 @@
         <v>148</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E188" s="8">
-        <v>46120</v>
-      </c>
-      <c r="F188" s="10"/>
-      <c r="G188" s="10"/>
+        <v>45742</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>1233</v>
+      </c>
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
     </row>
-    <row r="189" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>665</v>
       </c>
@@ -16817,21 +17488,25 @@
         <v>148</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E189" s="8">
-        <v>45728</v>
-      </c>
-      <c r="F189" s="10"/>
-      <c r="G189" s="10"/>
+        <v>45695</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G189" s="10" t="s">
+        <v>1235</v>
+      </c>
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
     </row>
-    <row r="190" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>668</v>
       </c>
@@ -16839,21 +17514,25 @@
         <v>148</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E190" s="8">
-        <v>45971</v>
-      </c>
-      <c r="F190" s="10"/>
-      <c r="G190" s="10"/>
+        <v>46120</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>1237</v>
+      </c>
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
     </row>
-    <row r="191" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>671</v>
       </c>
@@ -16861,21 +17540,25 @@
         <v>148</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E191" s="8">
-        <v>45887</v>
-      </c>
-      <c r="F191" s="10"/>
-      <c r="G191" s="10"/>
+        <v>45728</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G191" s="10" t="s">
+        <v>1239</v>
+      </c>
       <c r="H191" s="3"/>
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
     </row>
-    <row r="192" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>675</v>
       </c>
@@ -16883,21 +17566,25 @@
         <v>148</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E192" s="8">
-        <v>45742</v>
-      </c>
-      <c r="F192" s="10"/>
-      <c r="G192" s="10"/>
+        <v>45971</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>1241</v>
+      </c>
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
     </row>
-    <row r="193" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>677</v>
       </c>
@@ -16905,21 +17592,25 @@
         <v>148</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E193" s="8">
-        <v>45799</v>
-      </c>
-      <c r="F193" s="10"/>
-      <c r="G193" s="10"/>
+        <v>45887</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G193" s="10" t="s">
+        <v>1244</v>
+      </c>
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
     </row>
-    <row r="194" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>680</v>
       </c>
@@ -16927,21 +17618,25 @@
         <v>148</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D194" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E194" s="8">
-        <v>45971</v>
-      </c>
-      <c r="F194" s="10"/>
-      <c r="G194" s="10"/>
+        <v>45742</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>1246</v>
+      </c>
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
     </row>
-    <row r="195" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>683</v>
       </c>
@@ -16949,21 +17644,25 @@
         <v>148</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E195" s="8">
-        <v>45776</v>
-      </c>
-      <c r="F195" s="10"/>
-      <c r="G195" s="10"/>
+        <v>45799</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>1248</v>
+      </c>
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
     </row>
-    <row r="196" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>686</v>
       </c>
@@ -16971,21 +17670,25 @@
         <v>148</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E196" s="8">
-        <v>45832</v>
-      </c>
-      <c r="F196" s="10"/>
-      <c r="G196" s="10"/>
+        <v>45971</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>1249</v>
+      </c>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
     </row>
-    <row r="197" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>688</v>
       </c>
@@ -16993,21 +17696,25 @@
         <v>148</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E197" s="8">
-        <v>45701</v>
-      </c>
-      <c r="F197" s="10"/>
-      <c r="G197" s="10"/>
+        <v>45776</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>1251</v>
+      </c>
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
     </row>
-    <row r="198" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>691</v>
       </c>
@@ -17015,21 +17722,25 @@
         <v>148</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E198" s="8">
-        <v>45700</v>
-      </c>
-      <c r="F198" s="10"/>
-      <c r="G198" s="10"/>
+        <v>45832</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>1254</v>
+      </c>
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
     </row>
-    <row r="199" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>694</v>
       </c>
@@ -17037,21 +17748,25 @@
         <v>148</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E199" s="8">
-        <v>45700</v>
-      </c>
-      <c r="F199" s="10"/>
-      <c r="G199" s="10"/>
+        <v>45701</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G199" s="10" t="s">
+        <v>1255</v>
+      </c>
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
     </row>
-    <row r="200" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>697</v>
       </c>
@@ -17059,21 +17774,25 @@
         <v>148</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E200" s="8">
-        <v>45874</v>
-      </c>
-      <c r="F200" s="10"/>
-      <c r="G200" s="10"/>
+        <v>45700</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>1257</v>
+      </c>
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
     </row>
-    <row r="201" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>700</v>
       </c>
@@ -17081,21 +17800,25 @@
         <v>148</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E201" s="8">
-        <v>45734</v>
-      </c>
-      <c r="F201" s="10"/>
-      <c r="G201" s="10"/>
+        <v>45700</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>1259</v>
+      </c>
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>703</v>
       </c>
@@ -17103,21 +17826,25 @@
         <v>148</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E202" s="8">
-        <v>45699</v>
-      </c>
-      <c r="F202" s="10"/>
-      <c r="G202" s="10"/>
+        <v>45874</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G202" s="10" t="s">
+        <v>1261</v>
+      </c>
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
     </row>
-    <row r="203" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>706</v>
       </c>
@@ -17125,21 +17852,25 @@
         <v>148</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E203" s="8">
-        <v>45742</v>
-      </c>
-      <c r="F203" s="10"/>
-      <c r="G203" s="10"/>
+        <v>45734</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>1265</v>
+      </c>
       <c r="H203" s="3"/>
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
     </row>
-    <row r="204" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>709</v>
       </c>
@@ -17147,21 +17878,25 @@
         <v>148</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E204" s="8">
-        <v>45791</v>
-      </c>
-      <c r="F204" s="10"/>
-      <c r="G204" s="3"/>
+        <v>45699</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G204" s="10" t="s">
+        <v>1263</v>
+      </c>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
     </row>
-    <row r="205" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>712</v>
       </c>
@@ -17169,21 +17904,25 @@
         <v>148</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E205" s="8">
-        <v>45744</v>
-      </c>
-      <c r="F205" s="10"/>
-      <c r="G205" s="10"/>
+        <v>45742</v>
+      </c>
+      <c r="F205" s="10" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G205" s="10" t="s">
+        <v>1267</v>
+      </c>
       <c r="H205" s="3"/>
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
     </row>
-    <row r="206" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>715</v>
       </c>
@@ -17191,21 +17930,31 @@
         <v>148</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E206" s="8">
-        <v>45702</v>
-      </c>
-      <c r="F206" s="10"/>
-      <c r="G206" s="10"/>
-      <c r="H206" s="3"/>
-      <c r="I206" s="3"/>
-      <c r="J206" s="3"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+        <v>45791</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H206" s="10" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I206" s="10" t="s">
+        <v>1271</v>
+      </c>
+      <c r="J206" s="10" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>718</v>
       </c>
@@ -17213,21 +17962,31 @@
         <v>148</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E207" s="8">
-        <v>45740</v>
-      </c>
-      <c r="F207" s="10"/>
-      <c r="G207" s="10"/>
-      <c r="H207" s="3"/>
-      <c r="I207" s="3"/>
-      <c r="J207" s="3"/>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+        <v>45744</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H207" s="10" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I207" s="10" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J207" s="10" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>721</v>
       </c>
@@ -17235,21 +17994,25 @@
         <v>148</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E208" s="8">
-        <v>46104</v>
-      </c>
-      <c r="F208" s="10"/>
-      <c r="G208" s="10"/>
+        <v>45702</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>1278</v>
+      </c>
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
     </row>
-    <row r="209" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>724</v>
       </c>
@@ -17257,21 +18020,25 @@
         <v>148</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E209" s="8">
-        <v>45874</v>
-      </c>
-      <c r="F209" s="10"/>
-      <c r="G209" s="10"/>
+        <v>45740</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G209" s="10" t="s">
+        <v>1280</v>
+      </c>
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
     </row>
-    <row r="210" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>727</v>
       </c>
@@ -17279,21 +18046,25 @@
         <v>148</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E210" s="8">
-        <v>45720</v>
-      </c>
-      <c r="F210" s="10"/>
-      <c r="G210" s="10"/>
-      <c r="H210" s="10"/>
+        <v>46104</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G210" s="10" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H210" s="3"/>
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
     </row>
-    <row r="211" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>730</v>
       </c>
@@ -17301,21 +18072,25 @@
         <v>148</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E211" s="8">
-        <v>45695</v>
-      </c>
-      <c r="F211" s="10"/>
-      <c r="G211" s="10"/>
+        <v>45874</v>
+      </c>
+      <c r="F211" s="10" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G211" s="10" t="s">
+        <v>1284</v>
+      </c>
       <c r="H211" s="3"/>
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
     </row>
-    <row r="212" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>733</v>
       </c>
@@ -17323,21 +18098,27 @@
         <v>148</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E212" s="8">
-        <v>46188</v>
-      </c>
-      <c r="F212" s="10"/>
-      <c r="G212" s="10"/>
-      <c r="H212" s="3"/>
+        <v>45720</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G212" s="10" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H212" s="10" t="s">
+        <v>1287</v>
+      </c>
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
     </row>
-    <row r="213" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>736</v>
       </c>
@@ -17345,21 +18126,25 @@
         <v>148</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E213" s="8">
-        <v>45887</v>
-      </c>
-      <c r="F213" s="10"/>
-      <c r="G213" s="10"/>
+        <v>45695</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G213" s="10" t="s">
+        <v>1289</v>
+      </c>
       <c r="H213" s="3"/>
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
     </row>
-    <row r="214" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>739</v>
       </c>
@@ -17367,21 +18152,25 @@
         <v>148</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E214" s="8">
-        <v>45721</v>
-      </c>
-      <c r="F214" s="10"/>
-      <c r="G214" s="10"/>
+        <v>46188</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G214" s="10" t="s">
+        <v>1291</v>
+      </c>
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
     </row>
-    <row r="215" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>742</v>
       </c>
@@ -17389,21 +18178,25 @@
         <v>148</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E215" s="8">
-        <v>45700</v>
-      </c>
-      <c r="F215" s="10"/>
-      <c r="G215" s="10"/>
+        <v>45887</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G215" s="10" t="s">
+        <v>1293</v>
+      </c>
       <c r="H215" s="3"/>
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>745</v>
       </c>
@@ -17411,21 +18204,25 @@
         <v>148</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E216" s="8">
-        <v>45755</v>
-      </c>
-      <c r="F216" s="10"/>
-      <c r="G216" s="10"/>
+        <v>45721</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>1294</v>
+      </c>
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
     </row>
-    <row r="217" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>746</v>
       </c>
@@ -17433,65 +18230,77 @@
         <v>148</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E217" s="8">
-        <v>45804</v>
-      </c>
-      <c r="F217" s="10"/>
-      <c r="G217" s="10"/>
+        <v>45700</v>
+      </c>
+      <c r="F217" s="10" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G217" s="10" t="s">
+        <v>1296</v>
+      </c>
       <c r="H217" s="3"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
     </row>
-    <row r="218" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>751</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E218" s="8">
-        <v>45728</v>
-      </c>
-      <c r="F218" s="10"/>
-      <c r="G218" s="10"/>
+        <v>45755</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>1298</v>
+      </c>
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
     </row>
-    <row r="219" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>754</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E219" s="8">
-        <v>45727</v>
-      </c>
-      <c r="F219" s="10"/>
-      <c r="G219" s="10"/>
+        <v>45804</v>
+      </c>
+      <c r="F219" s="10" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>1300</v>
+      </c>
       <c r="H219" s="3"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>757</v>
       </c>
@@ -17499,21 +18308,25 @@
         <v>112</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E220" s="8">
-        <v>45698</v>
-      </c>
-      <c r="F220" s="10"/>
-      <c r="G220" s="10"/>
+        <v>45728</v>
+      </c>
+      <c r="F220" s="10" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>1303</v>
+      </c>
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
     </row>
-    <row r="221" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>760</v>
       </c>
@@ -17521,21 +18334,25 @@
         <v>112</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E221" s="8">
-        <v>45740</v>
-      </c>
-      <c r="F221" s="10"/>
-      <c r="G221" s="10"/>
+        <v>45727</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>1304</v>
+      </c>
       <c r="H221" s="3"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>764</v>
       </c>
@@ -17543,21 +18360,25 @@
         <v>112</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E222" s="8">
-        <v>45740</v>
-      </c>
-      <c r="F222" s="10"/>
-      <c r="G222" s="10"/>
+        <v>45698</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>1306</v>
+      </c>
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>766</v>
       </c>
@@ -17565,21 +18386,25 @@
         <v>112</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E223" s="8">
-        <v>45728</v>
-      </c>
-      <c r="F223" s="10"/>
-      <c r="G223" s="10"/>
+        <v>45740</v>
+      </c>
+      <c r="F223" s="10" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G223" s="10" t="s">
+        <v>1308</v>
+      </c>
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
     </row>
-    <row r="224" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>770</v>
       </c>
@@ -17587,21 +18412,25 @@
         <v>112</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E224" s="8">
-        <v>45727</v>
-      </c>
-      <c r="F224" s="10"/>
-      <c r="G224" s="10"/>
+        <v>45740</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G224" s="10" t="s">
+        <v>1310</v>
+      </c>
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
     </row>
-    <row r="225" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>773</v>
       </c>
@@ -17609,21 +18438,25 @@
         <v>112</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E225" s="8">
-        <v>45719</v>
-      </c>
-      <c r="F225" s="10"/>
-      <c r="G225" s="10"/>
+        <v>45728</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G225" s="10" t="s">
+        <v>1313</v>
+      </c>
       <c r="H225" s="3"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
     </row>
-    <row r="226" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>776</v>
       </c>
@@ -17631,21 +18464,25 @@
         <v>112</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E226" s="8">
-        <v>45936</v>
-      </c>
-      <c r="F226" s="10"/>
-      <c r="G226" s="10"/>
+        <v>45727</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G226" s="10" t="s">
+        <v>1314</v>
+      </c>
       <c r="H226" s="3"/>
       <c r="I226" s="3"/>
       <c r="J226" s="3"/>
     </row>
-    <row r="227" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>779</v>
       </c>
@@ -17653,21 +18490,25 @@
         <v>112</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E227" s="8">
-        <v>45813</v>
-      </c>
-      <c r="F227" s="10"/>
-      <c r="G227" s="10"/>
+        <v>45719</v>
+      </c>
+      <c r="F227" s="10" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G227" s="10" t="s">
+        <v>1316</v>
+      </c>
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
       <c r="J227" s="3"/>
     </row>
-    <row r="228" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>782</v>
       </c>
@@ -17675,21 +18516,25 @@
         <v>112</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E228" s="8">
-        <v>45813</v>
-      </c>
-      <c r="F228" s="10"/>
-      <c r="G228" s="10"/>
+        <v>45936</v>
+      </c>
+      <c r="F228" s="10" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G228" s="10" t="s">
+        <v>1319</v>
+      </c>
       <c r="H228" s="3"/>
       <c r="I228" s="3"/>
       <c r="J228" s="3"/>
     </row>
-    <row r="229" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>785</v>
       </c>
@@ -17697,7 +18542,7 @@
         <v>112</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>167</v>
@@ -17705,13 +18550,17 @@
       <c r="E229" s="8">
         <v>45813</v>
       </c>
-      <c r="F229" s="10"/>
-      <c r="G229" s="10"/>
+      <c r="F229" s="10" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G229" s="10" t="s">
+        <v>1321</v>
+      </c>
       <c r="H229" s="3"/>
       <c r="I229" s="3"/>
       <c r="J229" s="3"/>
     </row>
-    <row r="230" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>788</v>
       </c>
@@ -17719,7 +18568,7 @@
         <v>112</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>167</v>
@@ -17727,13 +18576,17 @@
       <c r="E230" s="8">
         <v>45813</v>
       </c>
-      <c r="F230" s="10"/>
-      <c r="G230" s="10"/>
+      <c r="F230" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G230" s="10" t="s">
+        <v>1322</v>
+      </c>
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
       <c r="J230" s="3"/>
     </row>
-    <row r="231" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>791</v>
       </c>
@@ -17741,21 +18594,25 @@
         <v>112</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E231" s="8">
-        <v>45812</v>
-      </c>
-      <c r="F231" s="10"/>
-      <c r="G231" s="10"/>
+        <v>45813</v>
+      </c>
+      <c r="F231" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G231" s="10" t="s">
+        <v>1323</v>
+      </c>
       <c r="H231" s="3"/>
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
     </row>
-    <row r="232" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>794</v>
       </c>
@@ -17763,21 +18620,25 @@
         <v>112</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E232" s="8">
-        <v>45812</v>
-      </c>
-      <c r="F232" s="10"/>
-      <c r="G232" s="10"/>
+        <v>45813</v>
+      </c>
+      <c r="F232" s="10" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G232" s="10" t="s">
+        <v>1325</v>
+      </c>
       <c r="H232" s="3"/>
       <c r="I232" s="3"/>
       <c r="J232" s="3"/>
     </row>
-    <row r="233" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>797</v>
       </c>
@@ -17785,21 +18646,25 @@
         <v>112</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E233" s="8">
-        <v>45813</v>
-      </c>
-      <c r="F233" s="10"/>
-      <c r="G233" s="10"/>
+        <v>45812</v>
+      </c>
+      <c r="F233" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G233" s="10" t="s">
+        <v>1327</v>
+      </c>
       <c r="H233" s="3"/>
       <c r="I233" s="3"/>
       <c r="J233" s="3"/>
     </row>
-    <row r="234" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>800</v>
       </c>
@@ -17807,21 +18672,25 @@
         <v>112</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E234" s="8">
-        <v>45813</v>
-      </c>
-      <c r="F234" s="10"/>
-      <c r="G234" s="10"/>
+        <v>45812</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G234" s="10" t="s">
+        <v>1329</v>
+      </c>
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
       <c r="J234" s="3"/>
     </row>
-    <row r="235" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>803</v>
       </c>
@@ -17829,21 +18698,25 @@
         <v>112</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E235" s="8">
-        <v>45698</v>
-      </c>
-      <c r="F235" s="10"/>
-      <c r="G235" s="10"/>
+        <v>45813</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G235" s="10" t="s">
+        <v>1331</v>
+      </c>
       <c r="H235" s="3"/>
       <c r="I235" s="3"/>
       <c r="J235" s="3"/>
     </row>
-    <row r="236" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>806</v>
       </c>
@@ -17851,21 +18724,25 @@
         <v>112</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E236" s="8">
-        <v>45698</v>
-      </c>
-      <c r="F236" s="10"/>
-      <c r="G236" s="10"/>
+        <v>45813</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G236" s="10" t="s">
+        <v>1333</v>
+      </c>
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
     </row>
-    <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>809</v>
       </c>
@@ -17873,7 +18750,7 @@
         <v>112</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>167</v>
@@ -17881,13 +18758,17 @@
       <c r="E237" s="8">
         <v>45698</v>
       </c>
-      <c r="F237" s="10"/>
-      <c r="G237" s="10"/>
+      <c r="F237" s="10" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G237" s="10" t="s">
+        <v>1336</v>
+      </c>
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
       <c r="J237" s="3"/>
     </row>
-    <row r="238" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>812</v>
       </c>
@@ -17895,7 +18776,7 @@
         <v>112</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>167</v>
@@ -17903,13 +18784,17 @@
       <c r="E238" s="8">
         <v>45698</v>
       </c>
-      <c r="F238" s="10"/>
-      <c r="G238" s="10"/>
+      <c r="F238" s="10" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G238" s="10" t="s">
+        <v>1337</v>
+      </c>
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
       <c r="J238" s="3"/>
     </row>
-    <row r="239" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>815</v>
       </c>
@@ -17917,21 +18802,25 @@
         <v>112</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E239" s="8">
-        <v>46003</v>
-      </c>
-      <c r="F239" s="10"/>
-      <c r="G239" s="10"/>
+        <v>45698</v>
+      </c>
+      <c r="F239" s="10" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G239" s="10" t="s">
+        <v>1339</v>
+      </c>
       <c r="H239" s="3"/>
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
     </row>
-    <row r="240" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>818</v>
       </c>
@@ -17939,21 +18828,25 @@
         <v>112</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E240" s="8">
-        <v>46002</v>
-      </c>
-      <c r="F240" s="10"/>
-      <c r="G240" s="10"/>
+        <v>45698</v>
+      </c>
+      <c r="F240" s="10" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G240" s="10" t="s">
+        <v>1341</v>
+      </c>
       <c r="H240" s="3"/>
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
     </row>
-    <row r="241" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>821</v>
       </c>
@@ -17961,21 +18854,25 @@
         <v>112</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E241" s="8">
-        <v>46002</v>
-      </c>
-      <c r="F241" s="10"/>
-      <c r="G241" s="10"/>
+        <v>46003</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G241" s="10" t="s">
+        <v>1343</v>
+      </c>
       <c r="H241" s="3"/>
       <c r="I241" s="3"/>
       <c r="J241" s="3"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>824</v>
       </c>
@@ -17983,21 +18880,25 @@
         <v>112</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E242" s="8">
-        <v>45699</v>
-      </c>
-      <c r="F242" s="10"/>
-      <c r="G242" s="10"/>
+        <v>46002</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G242" s="10" t="s">
+        <v>1345</v>
+      </c>
       <c r="H242" s="3"/>
       <c r="I242" s="3"/>
       <c r="J242" s="3"/>
     </row>
-    <row r="243" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>827</v>
       </c>
@@ -18005,21 +18906,25 @@
         <v>112</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E243" s="8">
-        <v>46003</v>
-      </c>
-      <c r="F243" s="10"/>
-      <c r="G243" s="10"/>
+        <v>46002</v>
+      </c>
+      <c r="F243" s="10" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G243" s="10" t="s">
+        <v>1347</v>
+      </c>
       <c r="H243" s="3"/>
       <c r="I243" s="3"/>
       <c r="J243" s="3"/>
     </row>
-    <row r="244" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>829</v>
       </c>
@@ -18027,21 +18932,25 @@
         <v>112</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E244" s="8">
-        <v>46003</v>
-      </c>
-      <c r="F244" s="10"/>
-      <c r="G244" s="10"/>
+        <v>45699</v>
+      </c>
+      <c r="F244" s="10" t="s">
+        <v>1350</v>
+      </c>
+      <c r="G244" s="10" t="s">
+        <v>1349</v>
+      </c>
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
       <c r="J244" s="3"/>
     </row>
-    <row r="245" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>833</v>
       </c>
@@ -18049,21 +18958,25 @@
         <v>112</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E245" s="8">
-        <v>45698</v>
-      </c>
-      <c r="F245" s="10"/>
-      <c r="G245" s="10"/>
+        <v>46003</v>
+      </c>
+      <c r="F245" s="10" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G245" s="10" t="s">
+        <v>1352</v>
+      </c>
       <c r="H245" s="3"/>
       <c r="I245" s="3"/>
       <c r="J245" s="3"/>
     </row>
-    <row r="246" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>837</v>
       </c>
@@ -18071,21 +18984,25 @@
         <v>112</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E246" s="8">
-        <v>45698</v>
-      </c>
-      <c r="F246" s="10"/>
-      <c r="G246" s="10"/>
+        <v>46003</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G246" s="10" t="s">
+        <v>1353</v>
+      </c>
       <c r="H246" s="3"/>
       <c r="I246" s="3"/>
       <c r="J246" s="3"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>839</v>
       </c>
@@ -18093,7 +19010,7 @@
         <v>112</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>167</v>
@@ -18101,13 +19018,17 @@
       <c r="E247" s="8">
         <v>45698</v>
       </c>
-      <c r="F247" s="10"/>
-      <c r="G247" s="10"/>
+      <c r="F247" s="10" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G247" s="10" t="s">
+        <v>1355</v>
+      </c>
       <c r="H247" s="3"/>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>842</v>
       </c>
@@ -18115,7 +19036,7 @@
         <v>112</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>167</v>
@@ -18123,13 +19044,17 @@
       <c r="E248" s="8">
         <v>45698</v>
       </c>
-      <c r="F248" s="10"/>
-      <c r="G248" s="10"/>
+      <c r="F248" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G248" s="10" t="s">
+        <v>1357</v>
+      </c>
       <c r="H248" s="3"/>
       <c r="I248" s="3"/>
       <c r="J248" s="3"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>845</v>
       </c>
@@ -18137,21 +19062,25 @@
         <v>112</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E249" s="8">
-        <v>45728</v>
-      </c>
-      <c r="F249" s="10"/>
-      <c r="G249" s="10"/>
+        <v>45698</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>1359</v>
+      </c>
+      <c r="G249" s="10" t="s">
+        <v>1360</v>
+      </c>
       <c r="H249" s="3"/>
       <c r="I249" s="3"/>
       <c r="J249" s="3"/>
     </row>
-    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>848</v>
       </c>
@@ -18159,22 +19088,78 @@
         <v>112</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>167</v>
       </c>
       <c r="E250" s="8">
-        <v>45699</v>
-      </c>
-      <c r="F250" s="10"/>
-      <c r="G250" s="10"/>
+        <v>45698</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G250" s="10" t="s">
+        <v>1361</v>
+      </c>
       <c r="H250" s="3"/>
       <c r="I250" s="3"/>
       <c r="J250" s="3"/>
     </row>
+    <row r="251" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E251" s="8">
+        <v>45728</v>
+      </c>
+      <c r="F251" s="10" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G251" s="10" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H251" s="3"/>
+      <c r="I251" s="3"/>
+      <c r="J251" s="3"/>
+    </row>
+    <row r="252" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E252" s="8">
+        <v>45699</v>
+      </c>
+      <c r="F252" s="10" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G252" s="10" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H252" s="3"/>
+      <c r="I252" s="3"/>
+      <c r="J252" s="3"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J250" xr:uid="{748BF04F-CFA1-4A20-9F03-257823D17D54}"/>
+  <autoFilter ref="A1:J252" xr:uid="{748BF04F-CFA1-4A20-9F03-257823D17D54}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{D83473F2-D59D-4B3D-93E8-C853EA321A34}"/>
@@ -18473,6 +19458,193 @@
     <hyperlink ref="F161" r:id="rId294" xr:uid="{55804FEF-C7D6-4995-ABB5-09CA72593618}"/>
     <hyperlink ref="G162" r:id="rId295" xr:uid="{C2A2EF5C-9D62-41CD-B9C3-86C3E315D1A5}"/>
     <hyperlink ref="F162" r:id="rId296" xr:uid="{4AA97056-C278-440F-9156-BB23288763D6}"/>
+    <hyperlink ref="G163" r:id="rId297" xr:uid="{F3AE13C6-4F2C-4D95-BB10-2E5D63597367}"/>
+    <hyperlink ref="F163" r:id="rId298" xr:uid="{9481CB7E-B7EE-4332-AE6E-EFCEA9D45174}"/>
+    <hyperlink ref="G164" r:id="rId299" xr:uid="{28F08E0D-92AA-428F-8595-A09D3146E47D}"/>
+    <hyperlink ref="F164" r:id="rId300" xr:uid="{F464ECC1-8648-4866-9174-03957AC3BC44}"/>
+    <hyperlink ref="G165" r:id="rId301" xr:uid="{959BFA93-177B-4DED-B3C9-2292F1694DFE}"/>
+    <hyperlink ref="F165" r:id="rId302" xr:uid="{CD31D630-A288-4404-A693-AA31E81B2167}"/>
+    <hyperlink ref="G166" r:id="rId303" xr:uid="{EA9165A6-1F05-4413-A034-7B8FA4CCE7E6}"/>
+    <hyperlink ref="F166" r:id="rId304" xr:uid="{671D6841-F94D-4A94-9761-9CB3CB933A79}"/>
+    <hyperlink ref="G167" r:id="rId305" xr:uid="{D6605730-F2B2-4101-84B9-2F7459E4D1A4}"/>
+    <hyperlink ref="H167" r:id="rId306" xr:uid="{8FDAB0AE-1EB5-44B6-A285-DA567AD8E02A}"/>
+    <hyperlink ref="F167" r:id="rId307" xr:uid="{679B6D81-D4C2-4F21-9E74-548AFE143ED9}"/>
+    <hyperlink ref="G168" r:id="rId308" xr:uid="{831F8140-E6EF-47E7-B2C7-0A236087B876}"/>
+    <hyperlink ref="H168" r:id="rId309" xr:uid="{0D8A26F9-8663-4076-AFCD-588C4C0F27EB}"/>
+    <hyperlink ref="F168" r:id="rId310" xr:uid="{56FFEF40-6281-4C07-8B16-2E413C41674B}"/>
+    <hyperlink ref="G169" r:id="rId311" xr:uid="{7179B10F-8E12-443C-A1F4-9FEFB1FBCC23}"/>
+    <hyperlink ref="F169" r:id="rId312" xr:uid="{66219702-4A26-4D91-96FD-EBE0FE6056C6}"/>
+    <hyperlink ref="F170" r:id="rId313" xr:uid="{6C3ADB45-5111-4B8B-AB42-41EB018B4F9D}"/>
+    <hyperlink ref="G170" r:id="rId314" xr:uid="{2B2D0DB7-2C09-4CB6-A647-1E07A2EEC37C}"/>
+    <hyperlink ref="G172" r:id="rId315" xr:uid="{1972AEB6-8B00-427C-A45F-02CE93D40EF8}"/>
+    <hyperlink ref="F172" r:id="rId316" xr:uid="{E2FC6558-C055-4FFC-8FA1-E06EB8D9EDC6}"/>
+    <hyperlink ref="F171" r:id="rId317" xr:uid="{9FF8924E-9278-4473-B6A7-590480271794}"/>
+    <hyperlink ref="F173" r:id="rId318" xr:uid="{6C3DA110-79F9-4805-A697-5E6549BEF9C9}"/>
+    <hyperlink ref="G173" r:id="rId319" xr:uid="{394DCDD4-F18C-4F19-B894-F73CCD0BB97A}"/>
+    <hyperlink ref="F174" r:id="rId320" xr:uid="{F0DB009C-A4A1-4F87-AA32-D4B2E800F38E}"/>
+    <hyperlink ref="G174" r:id="rId321" xr:uid="{166318D1-2865-45B3-93C7-9B9499D792AC}"/>
+    <hyperlink ref="F175" r:id="rId322" xr:uid="{CD5F4072-79E5-45C5-B760-6883F300DDC7}"/>
+    <hyperlink ref="G175" r:id="rId323" xr:uid="{BAA62F0F-3557-497D-AB59-2A580DB98609}"/>
+    <hyperlink ref="F176" r:id="rId324" xr:uid="{7941E9B2-3D72-4390-A3F9-EC135A501780}"/>
+    <hyperlink ref="G176" r:id="rId325" xr:uid="{027473BD-B655-4C1C-8700-6414F9531AA6}"/>
+    <hyperlink ref="G177" r:id="rId326" xr:uid="{9EE50501-5476-4987-8B43-CEBAD0A2957A}"/>
+    <hyperlink ref="F177" r:id="rId327" xr:uid="{861B361D-73EE-4BBA-9791-6C8760D45CF3}"/>
+    <hyperlink ref="G178" r:id="rId328" xr:uid="{40BB1B8F-A387-496F-846D-DD37B0869EA4}"/>
+    <hyperlink ref="F178" r:id="rId329" xr:uid="{AA1E9688-38E6-4554-865E-C9848C55FEDD}"/>
+    <hyperlink ref="G179" r:id="rId330" xr:uid="{794D26AA-1DFC-4FFD-B691-F221CF9EEEEE}"/>
+    <hyperlink ref="F179" r:id="rId331" xr:uid="{923CBAA1-88BD-48BE-A926-41900E1ED2B5}"/>
+    <hyperlink ref="F180" r:id="rId332" xr:uid="{C4B06723-0FBC-4888-9CC0-8E4C925E8390}"/>
+    <hyperlink ref="G180" r:id="rId333" xr:uid="{B77126D4-D1B4-4B51-8EF4-0EEEC835C84E}"/>
+    <hyperlink ref="G181" r:id="rId334" xr:uid="{766FD54E-C82A-4866-8713-28A0C098519E}"/>
+    <hyperlink ref="F181" r:id="rId335" xr:uid="{D91EF58E-18E2-40A9-85F3-27073D3A60C5}"/>
+    <hyperlink ref="G182" r:id="rId336" xr:uid="{BA2570DC-A95F-4016-8C39-9DD405926DDB}"/>
+    <hyperlink ref="F182" r:id="rId337" xr:uid="{F0253D01-F9B6-46B4-A6E6-8F0DBBC2EB8D}"/>
+    <hyperlink ref="G183" r:id="rId338" xr:uid="{0E41400C-C1EC-4124-96B5-F873A8431380}"/>
+    <hyperlink ref="F183" r:id="rId339" xr:uid="{F1ED9ED0-6AD4-4EE4-8327-0C533135519B}"/>
+    <hyperlink ref="F184" r:id="rId340" xr:uid="{CF13B49B-BD90-4E4D-A167-877874AFAF10}"/>
+    <hyperlink ref="G185" r:id="rId341" xr:uid="{CC7030A6-67A7-411A-B870-72C94BFD5B92}"/>
+    <hyperlink ref="F185" r:id="rId342" xr:uid="{8B519AD4-8354-4B1C-8B91-459438DAD1E0}"/>
+    <hyperlink ref="G186" r:id="rId343" xr:uid="{50C48576-5900-4334-919E-D06AB1ECB74F}"/>
+    <hyperlink ref="F186" r:id="rId344" xr:uid="{7BBEED55-02F5-4A65-B2F7-5C24D65E7D12}"/>
+    <hyperlink ref="G187" r:id="rId345" xr:uid="{671AB434-98AD-44E0-99AF-A5E68C49684D}"/>
+    <hyperlink ref="F187" r:id="rId346" xr:uid="{6F977D52-9728-452F-8B4E-B411D0F6F57D}"/>
+    <hyperlink ref="G188" r:id="rId347" xr:uid="{AE0F9430-52F9-4BEB-BC61-B732F1C25CE3}"/>
+    <hyperlink ref="F188" r:id="rId348" xr:uid="{AED496DC-1454-4791-8625-941A50A5F779}"/>
+    <hyperlink ref="G189" r:id="rId349" xr:uid="{69F6F723-8FB2-4C30-BCA2-1FD382AE98C9}"/>
+    <hyperlink ref="F189" r:id="rId350" xr:uid="{0A10A3CA-4BC9-4A8D-9F5D-3D3E4161E764}"/>
+    <hyperlink ref="G190" r:id="rId351" xr:uid="{A372209D-7448-454B-90A7-6333F08969F2}"/>
+    <hyperlink ref="F190" r:id="rId352" xr:uid="{40E23AD8-4E78-40E8-81D5-56A1F4108774}"/>
+    <hyperlink ref="G191" r:id="rId353" xr:uid="{D796FC6B-7AB6-41B3-A0C3-A8B4440C90F0}"/>
+    <hyperlink ref="F191" r:id="rId354" xr:uid="{CBD173C9-3AA0-464F-A75E-5CA3EB02BDCB}"/>
+    <hyperlink ref="G192" r:id="rId355" xr:uid="{C36BF623-9FEC-4D44-B82B-D73C0969687F}"/>
+    <hyperlink ref="F192" r:id="rId356" xr:uid="{55FB261A-FB4F-475A-B9F2-DE491E599FAD}"/>
+    <hyperlink ref="F193" r:id="rId357" xr:uid="{83F4F0D0-EC3F-40E4-B1AE-1DA3AE22637D}"/>
+    <hyperlink ref="G193" r:id="rId358" xr:uid="{3971BDD9-58A5-43F6-9CCF-5F0306F8EB8C}"/>
+    <hyperlink ref="F194" r:id="rId359" xr:uid="{421295BB-79BA-45FC-8238-FF12813B2CB5}"/>
+    <hyperlink ref="G194" r:id="rId360" xr:uid="{75A3E6A7-36DD-415B-864A-67CB9D57FC59}"/>
+    <hyperlink ref="F195" r:id="rId361" xr:uid="{9FF699E7-A37F-46A7-9669-B6ED1D85D9D7}"/>
+    <hyperlink ref="G195" r:id="rId362" xr:uid="{2BB0322C-79E0-4DC4-BE9F-C2A4FA8881B4}"/>
+    <hyperlink ref="G196" r:id="rId363" xr:uid="{E6520A9C-B882-445D-853F-345EFD0844F9}"/>
+    <hyperlink ref="F196" r:id="rId364" xr:uid="{076036D4-9447-4F5A-983D-28F11846F4CD}"/>
+    <hyperlink ref="G197" r:id="rId365" xr:uid="{D3B5FF56-3FDC-4277-8B30-3B68FA2F7E3E}"/>
+    <hyperlink ref="F197" r:id="rId366" xr:uid="{B5C8DC49-B5E1-4E85-99B7-BBCEE6C16CAE}"/>
+    <hyperlink ref="F198" r:id="rId367" xr:uid="{81746A15-B351-44B3-8279-3F862A455994}"/>
+    <hyperlink ref="G198" r:id="rId368" xr:uid="{D75EE564-7784-44E7-8DE8-D21AE26EE6B2}"/>
+    <hyperlink ref="G199" r:id="rId369" xr:uid="{3CF4F9AE-6A0C-4E0C-A20F-E96154E5063A}"/>
+    <hyperlink ref="F199" r:id="rId370" xr:uid="{DF594F4D-8842-4AFD-8D6C-62F9DE42D97A}"/>
+    <hyperlink ref="G200" r:id="rId371" xr:uid="{EEE0C389-7F29-4004-98A7-51DB7A0FE6A8}"/>
+    <hyperlink ref="F200" r:id="rId372" xr:uid="{EE725EC5-3A35-4E84-AEBF-1B1653663844}"/>
+    <hyperlink ref="G201" r:id="rId373" xr:uid="{1B8D2905-617C-4EF0-9A2C-6E83EDBEBD1F}"/>
+    <hyperlink ref="F201" r:id="rId374" xr:uid="{B73F25B6-35AB-4234-B1DC-F6F7D6166021}"/>
+    <hyperlink ref="G202" r:id="rId375" xr:uid="{1C3BBBA4-1E8B-49F2-B010-0108693902A0}"/>
+    <hyperlink ref="F202" r:id="rId376" xr:uid="{D4DCE9F6-A739-442B-9153-34A088871F3B}"/>
+    <hyperlink ref="G204" r:id="rId377" xr:uid="{9A189090-0F6D-4908-B3EB-544CF52F15A1}"/>
+    <hyperlink ref="F204" r:id="rId378" xr:uid="{B757922A-760D-4B8F-B6BD-6CD3D5991ECD}"/>
+    <hyperlink ref="G203" r:id="rId379" xr:uid="{3A6AB286-A9A1-41B8-9C88-05D550DB4590}"/>
+    <hyperlink ref="F203" r:id="rId380" xr:uid="{22FF4336-10E1-409C-9836-312348D74CC0}"/>
+    <hyperlink ref="G205" r:id="rId381" xr:uid="{DBF413D9-8B58-477B-8E7D-558D71CA5B54}"/>
+    <hyperlink ref="F205" r:id="rId382" xr:uid="{2F506778-8498-4D5F-93B6-92DE21872369}"/>
+    <hyperlink ref="G206" r:id="rId383" xr:uid="{E5564ABF-9E9F-48E8-961B-3BFF7B367437}"/>
+    <hyperlink ref="H206" r:id="rId384" xr:uid="{0005F0D0-BDEB-429D-86BD-ED2CAF961273}"/>
+    <hyperlink ref="I206" r:id="rId385" xr:uid="{728E687F-EEC2-4162-B566-BE8732325ED0}"/>
+    <hyperlink ref="J206" r:id="rId386" xr:uid="{71645601-0F88-4534-BB85-51C6A614942C}"/>
+    <hyperlink ref="F206" r:id="rId387" xr:uid="{172054D6-D163-41D7-8791-2A9EF2CE0F3A}"/>
+    <hyperlink ref="G207" r:id="rId388" xr:uid="{0C9395C6-3E7D-4F88-AC55-DB3CE394B121}"/>
+    <hyperlink ref="H207" r:id="rId389" xr:uid="{5C21ABCD-A328-480F-8F55-D82C5474F25E}"/>
+    <hyperlink ref="F207" r:id="rId390" xr:uid="{5EE9A6CB-A9F0-452C-91ED-E5E62C37CEBB}"/>
+    <hyperlink ref="I207" r:id="rId391" xr:uid="{4F505362-3621-4D25-A9BA-4A2CF7470746}"/>
+    <hyperlink ref="J207" r:id="rId392" xr:uid="{AEB4E477-2A53-4FA6-B1B2-72A38F8F9710}"/>
+    <hyperlink ref="G208" r:id="rId393" xr:uid="{EF01C0E1-4913-49DE-8CE5-1AB344915CED}"/>
+    <hyperlink ref="F208" r:id="rId394" xr:uid="{9482F99D-4F9A-4027-976B-E865CDD2BF3E}"/>
+    <hyperlink ref="G209" r:id="rId395" xr:uid="{9D7E8AEC-406D-4A7A-91D3-EDD3D036D01E}"/>
+    <hyperlink ref="F209" r:id="rId396" xr:uid="{08E8DE93-4022-4F33-BF24-5FD74DF048A5}"/>
+    <hyperlink ref="G210" r:id="rId397" xr:uid="{E5DBF6EC-CE71-4D00-904B-A574D2D9830A}"/>
+    <hyperlink ref="F210" r:id="rId398" xr:uid="{8B1FD8D0-2F0C-4A01-83DE-263592BD7E69}"/>
+    <hyperlink ref="G211" r:id="rId399" xr:uid="{39E51CDD-2922-40DC-9971-266E485C945A}"/>
+    <hyperlink ref="F211" r:id="rId400" xr:uid="{48F6EEBE-0181-454F-95E1-BF7D79D6A2F7}"/>
+    <hyperlink ref="G212" r:id="rId401" xr:uid="{2E8E5B0C-E808-4008-A0CF-119E03B18CA0}"/>
+    <hyperlink ref="H212" r:id="rId402" xr:uid="{DEB5A549-5B8E-4E99-A144-DA2C561F25FD}"/>
+    <hyperlink ref="F212" r:id="rId403" xr:uid="{C2E3FF6B-E719-45A2-85BA-C4BA9F68AD8D}"/>
+    <hyperlink ref="G213" r:id="rId404" xr:uid="{C4330736-A01A-4724-B844-5B250CB49463}"/>
+    <hyperlink ref="F213" r:id="rId405" xr:uid="{42BA6D3F-BEA5-403B-9DDE-F6485FEE0DB7}"/>
+    <hyperlink ref="G214" r:id="rId406" xr:uid="{EA9DDFDB-CCFA-4B96-956E-A49845996EE8}"/>
+    <hyperlink ref="F214" r:id="rId407" xr:uid="{0556FC94-688D-4AD4-B99B-D6553B3A4243}"/>
+    <hyperlink ref="G215" r:id="rId408" xr:uid="{6688218D-BA82-45F4-8DF1-6D3EA391EE1D}"/>
+    <hyperlink ref="F215" r:id="rId409" xr:uid="{8C28527F-B772-4D54-9BCB-6BB270C70059}"/>
+    <hyperlink ref="G216" r:id="rId410" xr:uid="{4801E235-33E7-4DD9-A8FA-6A756F9911E3}"/>
+    <hyperlink ref="F216" r:id="rId411" xr:uid="{B4F72158-1200-4628-AB4E-3FBEA56EFE00}"/>
+    <hyperlink ref="G217" r:id="rId412" xr:uid="{0E252782-1457-47D0-8AE6-FCBF5835B424}"/>
+    <hyperlink ref="F217" r:id="rId413" xr:uid="{E1F2BE1E-3F04-43CA-87F5-55C2E22FC97B}"/>
+    <hyperlink ref="G218" r:id="rId414" xr:uid="{83C0BD34-03D2-4D66-9808-019551C9185D}"/>
+    <hyperlink ref="F218" r:id="rId415" xr:uid="{09375163-044C-49E3-82D0-D337F2348671}"/>
+    <hyperlink ref="G219" r:id="rId416" xr:uid="{13F26368-D677-4057-AF3D-CE07AEA86B17}"/>
+    <hyperlink ref="F219" r:id="rId417" xr:uid="{0ED951B9-BFD1-4C50-AB0F-8F81BF61CE3C}"/>
+    <hyperlink ref="F220" r:id="rId418" xr:uid="{3BBBE43D-8D61-497D-9020-2D8AFF80AD2C}"/>
+    <hyperlink ref="G220" r:id="rId419" xr:uid="{B5F30732-601E-47A8-8F88-9D7035E45B52}"/>
+    <hyperlink ref="G221" r:id="rId420" xr:uid="{2CC86228-0C0A-4B2F-92DC-5BBF743DD9AF}"/>
+    <hyperlink ref="F221" r:id="rId421" xr:uid="{FB0D2C57-9EA1-4503-A7FF-F21B098DC6A3}"/>
+    <hyperlink ref="G222" r:id="rId422" xr:uid="{8D75F301-71B7-48F7-B353-B63E5A2D59BB}"/>
+    <hyperlink ref="F222" r:id="rId423" xr:uid="{C6343AB0-E805-48A4-A593-8D3339F20E7D}"/>
+    <hyperlink ref="G223" r:id="rId424" xr:uid="{6A0785EF-EE17-450D-B7BA-3F7E8CDF79DA}"/>
+    <hyperlink ref="F223" r:id="rId425" xr:uid="{CB219645-EB3D-4F4B-A696-719518C436A8}"/>
+    <hyperlink ref="G224" r:id="rId426" xr:uid="{0699AE51-5D8C-401D-9D02-3FFD77C7064C}"/>
+    <hyperlink ref="F224" r:id="rId427" xr:uid="{304D5B19-F9E3-4C94-AA41-2AFC717E7909}"/>
+    <hyperlink ref="F225" r:id="rId428" xr:uid="{0A39901E-1283-42D8-90A0-BD5754807423}"/>
+    <hyperlink ref="G225" r:id="rId429" xr:uid="{22843AD8-298B-4922-9A19-4B05FC40BBC2}"/>
+    <hyperlink ref="G226" r:id="rId430" xr:uid="{9A441C44-C8AD-4A4E-88F8-00E78B4D2969}"/>
+    <hyperlink ref="F226" r:id="rId431" xr:uid="{BDC03C53-3758-4430-89B1-B1AC8A8F6362}"/>
+    <hyperlink ref="G227" r:id="rId432" xr:uid="{7BD561AC-DD4D-4E23-BF37-C65C78B0E211}"/>
+    <hyperlink ref="F227" r:id="rId433" xr:uid="{958DF405-4FB2-4573-B7EE-3FD3F5639522}"/>
+    <hyperlink ref="F228" r:id="rId434" xr:uid="{F3CBE438-B1F3-4705-81D9-2CBD756F8AD8}"/>
+    <hyperlink ref="G228" r:id="rId435" xr:uid="{8A57DBE0-0662-4915-904B-19A7E6EF0ADC}"/>
+    <hyperlink ref="F229" r:id="rId436" xr:uid="{5F7B796D-92D9-4992-BC28-9C13ED803807}"/>
+    <hyperlink ref="G229" r:id="rId437" xr:uid="{31163F01-F35C-4D8B-8527-C4E33540A95C}"/>
+    <hyperlink ref="G230" r:id="rId438" xr:uid="{810053C1-F333-472D-9AF8-6AC37BCA42B1}"/>
+    <hyperlink ref="F230" r:id="rId439" xr:uid="{8255CE20-4EB9-469B-8578-42029FB82E1C}"/>
+    <hyperlink ref="G231" r:id="rId440" xr:uid="{D402A84E-DADB-4A42-8FD3-4704EE134BBA}"/>
+    <hyperlink ref="F231" r:id="rId441" xr:uid="{FCC3AD10-663D-47B0-AE50-1B8042867C9A}"/>
+    <hyperlink ref="G232" r:id="rId442" xr:uid="{2D612948-D2F5-4165-8C55-651A98C04D52}"/>
+    <hyperlink ref="F232" r:id="rId443" xr:uid="{8FA91398-5DF0-461C-9455-9A65C4F6E7F9}"/>
+    <hyperlink ref="G233" r:id="rId444" xr:uid="{0BA9037E-F3CA-4038-8135-7B1D33A78393}"/>
+    <hyperlink ref="F233" r:id="rId445" xr:uid="{D0904DC4-C928-4631-9505-FF83FC934D52}"/>
+    <hyperlink ref="G234" r:id="rId446" xr:uid="{4955CD3D-3441-48D6-ADA5-9DE03D5ABD9A}"/>
+    <hyperlink ref="F234" r:id="rId447" xr:uid="{C7D94E5B-30E1-48C9-935F-196FD8C6266C}"/>
+    <hyperlink ref="G235" r:id="rId448" xr:uid="{3400A7B1-87F4-4E71-AFA0-F01745081B9A}"/>
+    <hyperlink ref="F235" r:id="rId449" xr:uid="{AC0944AB-D133-4967-A68E-95B52262D926}"/>
+    <hyperlink ref="G236" r:id="rId450" xr:uid="{5CD4B550-7342-401C-959A-ED68527FB243}"/>
+    <hyperlink ref="F236" r:id="rId451" xr:uid="{DEDA7193-7434-4558-9CC4-749C90A117D0}"/>
+    <hyperlink ref="F237" r:id="rId452" xr:uid="{DF8E7BC8-CCFF-4C27-85E1-859B82F8AE98}"/>
+    <hyperlink ref="G237" r:id="rId453" xr:uid="{892D5AF6-F545-415D-A159-F039E9C03793}"/>
+    <hyperlink ref="G238" r:id="rId454" xr:uid="{133D914F-1496-4D73-A10C-B5B489A3B1D6}"/>
+    <hyperlink ref="F238" r:id="rId455" xr:uid="{F3DB1AC5-F20F-48EE-B536-16185B4C15D1}"/>
+    <hyperlink ref="G239" r:id="rId456" xr:uid="{21582881-2E4D-4F2E-9FAF-9345E32801EB}"/>
+    <hyperlink ref="F239" r:id="rId457" xr:uid="{673C0D23-F496-4106-B1A1-2A716D320C39}"/>
+    <hyperlink ref="G240" r:id="rId458" xr:uid="{C310127A-9016-447F-99E8-0952BF17D51D}"/>
+    <hyperlink ref="F240" r:id="rId459" xr:uid="{5DFB8B04-CE0D-4CCE-BD39-8B30E8D647C0}"/>
+    <hyperlink ref="G241" r:id="rId460" xr:uid="{577668A6-531E-47D8-A762-C9E8D1E6D2C8}"/>
+    <hyperlink ref="F241" r:id="rId461" xr:uid="{E5C0F342-26B9-43C4-BB7B-D9A532258D2E}"/>
+    <hyperlink ref="G242" r:id="rId462" xr:uid="{24B9B876-17D8-47C1-912C-3658A8AB8B41}"/>
+    <hyperlink ref="F242" r:id="rId463" xr:uid="{18C78DE9-48C1-4B50-AB70-533B43AE3CF2}"/>
+    <hyperlink ref="G243" r:id="rId464" xr:uid="{1C88A58A-3432-4635-A063-AD0E3F718283}"/>
+    <hyperlink ref="F243" r:id="rId465" xr:uid="{D2E31C80-44BC-497C-904F-8ED53D87D86F}"/>
+    <hyperlink ref="G244" r:id="rId466" xr:uid="{19BB7520-A60A-46F2-BF46-8A10300A7CC7}"/>
+    <hyperlink ref="F244" r:id="rId467" xr:uid="{C1F84B5C-6C12-4A51-A30C-E47728CF6294}"/>
+    <hyperlink ref="F245" r:id="rId468" xr:uid="{4D9D1EC8-A09F-4FC7-A521-E939340B0D96}"/>
+    <hyperlink ref="G245" r:id="rId469" xr:uid="{01C65493-FB71-4960-9544-6C88C79AD990}"/>
+    <hyperlink ref="G246" r:id="rId470" xr:uid="{B49F09D8-0973-4518-A328-EACA78CB253D}"/>
+    <hyperlink ref="F246" r:id="rId471" xr:uid="{EF902AEB-C29B-4DF0-AEB8-A38B246D8D90}"/>
+    <hyperlink ref="G247" r:id="rId472" xr:uid="{D5912C10-0370-4F66-99A4-2AE4719E0956}"/>
+    <hyperlink ref="F247" r:id="rId473" xr:uid="{44D7B143-159B-4C1B-8226-F721CAA57DDA}"/>
+    <hyperlink ref="G248" r:id="rId474" xr:uid="{9EB1C09B-90AF-4F5A-A860-024BA47C7EFC}"/>
+    <hyperlink ref="F248" r:id="rId475" xr:uid="{99E7DA75-8613-4B5F-BADE-B4B240796DEC}"/>
+    <hyperlink ref="F249" r:id="rId476" xr:uid="{AA11CD8A-F9B7-40B8-8BAD-4833B87A6DE7}"/>
+    <hyperlink ref="G249" r:id="rId477" xr:uid="{8A2C9D61-F14D-4271-809C-73156B31E5D1}"/>
+    <hyperlink ref="G250" r:id="rId478" xr:uid="{5E16DCF4-DAF3-45A7-9ECA-F642597785A7}"/>
+    <hyperlink ref="F250" r:id="rId479" xr:uid="{CA1CF02D-D0C0-45CB-A2A8-1AA134C2DB75}"/>
+    <hyperlink ref="G251" r:id="rId480" xr:uid="{7DC06E17-CF19-43CB-8C4D-0D2641F9ABDA}"/>
+    <hyperlink ref="F251" r:id="rId481" xr:uid="{451D9DD0-9089-41F4-B834-1310A55A4565}"/>
+    <hyperlink ref="G252" r:id="rId482" xr:uid="{F9037714-0D65-4CF9-A319-42BA8E739225}"/>
+    <hyperlink ref="F252" r:id="rId483" xr:uid="{693F0EF6-C943-42E6-8450-971BE8B31518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
